--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Synonymes RPPS : InscriptionOrdre</t>
+    <t>Synonymes : InscriptionOrdre</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -458,9 +458,6 @@
     <t>Période durant laquelle la personne est autorisée à exercer la profession pour laquelle elle a été inscrite.</t>
   </si>
   <si>
-    <t>Synonyme : periodValidite</t>
-  </si>
-  <si>
     <t>Extension.extension:period.id</t>
   </si>
   <si>
@@ -539,7 +536,7 @@
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateRadiation</t>
+    <t>Synonyme : dateRadiation</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -2696,9 +2693,7 @@
       <c r="M17" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -2767,7 +2762,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>106</v>
@@ -2870,7 +2865,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>108</v>
@@ -2973,7 +2968,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>110</v>
@@ -3078,7 +3073,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>117</v>
@@ -3104,7 +3099,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>119</v>
@@ -3179,13 +3174,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>117</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>74</v>
@@ -3207,7 +3202,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>119</v>
@@ -3284,10 +3279,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3387,10 +3382,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3492,10 +3487,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3515,19 +3510,19 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3577,30 +3572,30 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI25" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3620,72 +3615,72 @@
         <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K26" t="s" s="2">
-        <v>159</v>
-      </c>
       <c r="L26" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q26" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="R26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>172</v>
-      </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
@@ -3693,24 +3688,24 @@
         <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>74</v>
@@ -3735,13 +3730,13 @@
         <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3811,7 +3806,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>106</v>
@@ -3914,7 +3909,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>108</v>
@@ -4017,7 +4012,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>110</v>
@@ -4060,7 +4055,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>74</v>
@@ -4122,7 +4117,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>117</v>
@@ -4223,7 +4218,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>117</v>
@@ -4287,10 +4282,10 @@
         <v>127</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4328,13 +4323,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>74</v>
@@ -4359,13 +4354,13 @@
         <v>90</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4435,7 +4430,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>106</v>
@@ -4538,7 +4533,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>108</v>
@@ -4641,7 +4636,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>110</v>
@@ -4684,7 +4679,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>74</v>
@@ -4746,7 +4741,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>117</v>
@@ -4847,7 +4842,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>117</v>
@@ -4952,13 +4947,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>74</v>
@@ -4983,13 +4978,13 @@
         <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5059,7 +5054,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>106</v>
@@ -5162,7 +5157,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>108</v>
@@ -5265,7 +5260,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>110</v>
@@ -5308,7 +5303,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>74</v>
@@ -5370,7 +5365,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>117</v>
@@ -5396,7 +5391,7 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>119</v>
@@ -5604,7 +5599,7 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>119</v>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
